--- a/RUBRICS.xlsx
+++ b/RUBRICS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\IIT M\HMS_24F2007159\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E7905E-EF5A-4408-ACE5-479D0847B8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4684B09E-F144-43F2-8296-8A185BA06135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
@@ -133,6 +133,24 @@
   </si>
   <si>
     <t>Admin - can view upcomming appointments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctor Dashboard </t>
+  </si>
+  <si>
+    <t>Admin DAShboard Correction</t>
+  </si>
+  <si>
+    <t>Notes should have dfates</t>
+  </si>
+  <si>
+    <t>Adminj Dashboard - Patinet - View History Button</t>
+  </si>
+  <si>
+    <t>Search results shoud have buttons</t>
+  </si>
+  <si>
+    <t>Pat Dashboard - Searc function - Department doctors</t>
   </si>
 </sst>
 </file>
@@ -148,7 +166,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -167,6 +185,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -180,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -190,11 +220,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -202,16 +234,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -501,15 +523,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:E42"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="148.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="148.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -523,7 +545,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -537,7 +559,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B4" s="4">
         <v>2</v>
       </c>
@@ -551,7 +573,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B5" s="4">
         <v>3</v>
       </c>
@@ -565,7 +587,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>4</v>
       </c>
@@ -576,10 +598,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>5</v>
       </c>
@@ -593,7 +615,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B8" s="4">
         <v>6</v>
       </c>
@@ -607,7 +629,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B9" s="4">
         <v>7</v>
       </c>
@@ -621,7 +643,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
         <v>8</v>
       </c>
@@ -633,7 +655,7 @@
       </c>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B11" s="4">
         <v>9</v>
       </c>
@@ -645,7 +667,7 @@
       </c>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B12" s="4">
         <v>10</v>
       </c>
@@ -657,7 +679,7 @@
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B13" s="4">
         <v>11</v>
       </c>
@@ -671,7 +693,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B14" s="4">
         <v>12</v>
       </c>
@@ -683,7 +705,7 @@
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B15" s="4">
         <v>13</v>
       </c>
@@ -697,7 +719,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B16" s="4">
         <v>14</v>
       </c>
@@ -711,7 +733,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="4">
         <v>15</v>
       </c>
@@ -725,7 +747,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B18" s="4">
         <v>16</v>
       </c>
@@ -739,7 +761,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="4">
         <v>17</v>
       </c>
@@ -751,7 +773,7 @@
       </c>
       <c r="E19" s="4"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B20" s="4">
         <v>18</v>
       </c>
@@ -763,7 +785,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B21" s="4">
         <v>19</v>
       </c>
@@ -775,7 +797,7 @@
       </c>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B22" s="4">
         <v>20</v>
       </c>
@@ -787,7 +809,7 @@
       </c>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B23" s="4">
         <v>21</v>
       </c>
@@ -799,7 +821,7 @@
       </c>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B24" s="4">
         <v>22</v>
       </c>
@@ -811,7 +833,7 @@
       </c>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B25" s="4">
         <v>23</v>
       </c>
@@ -823,7 +845,7 @@
       </c>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B26" s="4">
         <v>24</v>
       </c>
@@ -835,37 +857,67 @@
       </c>
       <c r="E26" s="4"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C30" t="s">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C30" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C31" t="s">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" t="s">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C34" s="5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C37" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C38" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C40" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C41" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C42" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>$E$3</formula>
     </cfRule>
   </conditionalFormatting>

--- a/RUBRICS.xlsx
+++ b/RUBRICS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\IIT M\HMS_24F2007159\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4684B09E-F144-43F2-8296-8A185BA06135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDE3D31-E575-4E18-A7B9-57A87BE79147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -109,9 +109,6 @@
   </si>
   <si>
     <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>date Storage / Trime storage to be sorted</t>
@@ -166,7 +163,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,12 +173,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -210,18 +201,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,25 +532,25 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4" t="s">
@@ -569,12 +559,12 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
       <c r="C5" t="s">
@@ -583,26 +573,26 @@
       <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
       <c r="C7" t="s">
@@ -611,12 +601,12 @@
       <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
       <c r="C8" t="s">
@@ -625,12 +615,12 @@
       <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>28</v>
+      <c r="E8" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>7</v>
       </c>
       <c r="C9" t="s">
@@ -639,12 +629,12 @@
       <c r="D9" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" t="s">
@@ -653,10 +643,12 @@
       <c r="D10" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>9</v>
       </c>
       <c r="C11" t="s">
@@ -665,10 +657,12 @@
       <c r="D11" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>10</v>
       </c>
       <c r="C12" t="s">
@@ -677,10 +671,12 @@
       <c r="D12" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>11</v>
       </c>
       <c r="C13" t="s">
@@ -689,12 +685,12 @@
       <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>12</v>
       </c>
       <c r="C14" t="s">
@@ -703,10 +699,12 @@
       <c r="D14" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>13</v>
       </c>
       <c r="C15" t="s">
@@ -715,12 +713,12 @@
       <c r="D15" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>14</v>
       </c>
       <c r="C16" t="s">
@@ -729,12 +727,12 @@
       <c r="D16" t="b">
         <v>1</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>15</v>
       </c>
       <c r="C17" t="s">
@@ -743,12 +741,12 @@
       <c r="D17" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>16</v>
       </c>
       <c r="C18" t="s">
@@ -757,12 +755,12 @@
       <c r="D18" t="b">
         <v>1</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B19" s="4">
+      <c r="B19" s="3">
         <v>17</v>
       </c>
       <c r="C19" t="s">
@@ -771,10 +769,12 @@
       <c r="D19" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B20" s="4">
+      <c r="B20" s="3">
         <v>18</v>
       </c>
       <c r="C20" t="s">
@@ -783,10 +783,12 @@
       <c r="D20" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="4"/>
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B21" s="4">
+      <c r="B21" s="3">
         <v>19</v>
       </c>
       <c r="C21" t="s">
@@ -795,10 +797,12 @@
       <c r="D21" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="4"/>
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>20</v>
       </c>
       <c r="C22" t="s">
@@ -807,10 +811,12 @@
       <c r="D22" t="b">
         <v>1</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B23" s="4">
+      <c r="B23" s="3">
         <v>21</v>
       </c>
       <c r="C23" t="s">
@@ -819,10 +825,10 @@
       <c r="D23" t="b">
         <v>1</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B24" s="4">
+      <c r="B24" s="3">
         <v>22</v>
       </c>
       <c r="C24" t="s">
@@ -831,10 +837,10 @@
       <c r="D24" t="b">
         <v>1</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>23</v>
       </c>
       <c r="C25" t="s">
@@ -843,10 +849,10 @@
       <c r="D25" t="b">
         <v>1</v>
       </c>
-      <c r="E25" s="4"/>
+      <c r="E25" s="3"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B26" s="4">
+      <c r="B26" s="3">
         <v>24</v>
       </c>
       <c r="C26" t="s">
@@ -855,64 +861,64 @@
       <c r="D26" t="b">
         <v>1</v>
       </c>
-      <c r="E26" s="4"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="C31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C37" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C37" s="5" t="s">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C38" s="4" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C38" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="39" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C40" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C40" s="5" t="s">
+    <row r="41" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C41" s="4" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C41" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="42" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
